--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/SOUTH_CAROLINA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/SOUTH_CAROLINA_2019.xlsx
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C135">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C226">
@@ -5593,7 +5593,7 @@
         <v>61</v>
       </c>
       <c r="D291">
-        <v>0.009046418508082455</v>
+        <v>0.009046418508082457</v>
       </c>
     </row>
     <row r="292">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C618">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C645">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C652">
